--- a/01-delivered-case-studies/taash-tax-automation/Excel/Project_Workbook.xlsx
+++ b/01-delivered-case-studies/taash-tax-automation/Excel/Project_Workbook.xlsx
@@ -492,7 +492,7 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Founder and Product Business Analyst</t>
+          <t>Business Analyst (Contract)</t>
         </is>
       </c>
     </row>
